--- a/data/Format=XLSX/Model=M10+/Floor=2/Location=Patio/Device=01/M10+_device01_11-10-2024 17:00:36.xlsx
+++ b/data/Format=XLSX/Model=M10+/Floor=2/Location=Patio/Device=01/M10+_device01_11-10-2024 17:00:36.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11110"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jack/Downloads/M10+_device01_11-10-2024 17:00:"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jack/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7553279-7693-2D45-A0FF-67B66CE82A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D7AA5F-840A-5740-8A11-DC5D3BBB49F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="880" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="607">
   <si>
     <t>NO.</t>
   </si>
@@ -1328,6 +1328,12 @@
   </si>
   <si>
     <t>24.8</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>2024-11-10 15:00:00(+08:00)</t>
   </si>
   <si>
     <t>AQI</t>
@@ -2186,7 +2192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:H170"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.33203125" bestFit="1" customWidth="1"/>
@@ -2210,19 +2216,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -2239,13 +2245,13 @@
         <v>106</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>148</v>
@@ -2265,13 +2271,13 @@
         <v>106</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>146</v>
@@ -2291,13 +2297,13 @@
         <v>89</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>148</v>
@@ -2317,13 +2323,13 @@
         <v>159</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>146</v>
@@ -2343,13 +2349,13 @@
         <v>153</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>153</v>
@@ -2369,13 +2375,13 @@
         <v>146</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>151</v>
@@ -2395,13 +2401,13 @@
         <v>151</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>151</v>
@@ -2421,13 +2427,13 @@
         <v>141</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>153</v>
@@ -2447,13 +2453,13 @@
         <v>143</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>159</v>
@@ -2473,13 +2479,13 @@
         <v>146</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>164</v>
@@ -2499,13 +2505,13 @@
         <v>148</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>166</v>
@@ -2525,13 +2531,13 @@
         <v>148</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>166</v>
@@ -2551,13 +2557,13 @@
         <v>146</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>166</v>
@@ -2577,13 +2583,13 @@
         <v>136</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>166</v>
@@ -2603,13 +2609,13 @@
         <v>122</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>166</v>
@@ -2629,13 +2635,13 @@
         <v>122</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>166</v>
@@ -2655,7 +2661,7 @@
         <v>115</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>139</v>
@@ -2681,7 +2687,7 @@
         <v>115</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>139</v>
@@ -2707,13 +2713,13 @@
         <v>112</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>143</v>
@@ -2733,13 +2739,13 @@
         <v>136</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>141</v>
@@ -2759,13 +2765,13 @@
         <v>136</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>109</v>
@@ -2785,13 +2791,13 @@
         <v>124</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>91</v>
@@ -2811,13 +2817,13 @@
         <v>77</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>109</v>
@@ -2837,13 +2843,13 @@
         <v>146</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>133</v>
@@ -2863,13 +2869,13 @@
         <v>143</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>139</v>
@@ -2889,13 +2895,13 @@
         <v>173</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>143</v>
@@ -2915,13 +2921,13 @@
         <v>91</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>130</v>
@@ -2941,13 +2947,13 @@
         <v>57</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>109</v>
@@ -2967,13 +2973,13 @@
         <v>60</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>112</v>
@@ -2993,13 +2999,13 @@
         <v>62</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>115</v>
@@ -3019,13 +3025,13 @@
         <v>89</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>122</v>
@@ -3045,13 +3051,13 @@
         <v>112</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>122</v>
@@ -3071,13 +3077,13 @@
         <v>112</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>117</v>
@@ -3097,13 +3103,13 @@
         <v>106</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>122</v>
@@ -3123,13 +3129,13 @@
         <v>93</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>127</v>
@@ -3149,13 +3155,13 @@
         <v>74</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>122</v>
@@ -3175,13 +3181,13 @@
         <v>68</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>117</v>
@@ -3201,13 +3207,13 @@
         <v>57</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>109</v>
@@ -3227,13 +3233,13 @@
         <v>43</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>112</v>
@@ -3253,13 +3259,13 @@
         <v>32</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>117</v>
@@ -3279,13 +3285,13 @@
         <v>32</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>109</v>
@@ -3305,13 +3311,13 @@
         <v>32</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>112</v>
@@ -3331,13 +3337,13 @@
         <v>60</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>112</v>
@@ -3357,13 +3363,13 @@
         <v>62</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>106</v>
@@ -3383,13 +3389,13 @@
         <v>184</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>71</v>
@@ -3409,13 +3415,13 @@
         <v>117</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>71</v>
@@ -3435,13 +3441,13 @@
         <v>40</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>71</v>
@@ -3461,13 +3467,13 @@
         <v>32</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>83</v>
@@ -3487,13 +3493,13 @@
         <v>37</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>97</v>
@@ -3513,13 +3519,13 @@
         <v>32</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>115</v>
@@ -3539,13 +3545,13 @@
         <v>37</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>151</v>
@@ -3565,13 +3571,13 @@
         <v>164</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>164</v>
@@ -3591,13 +3597,13 @@
         <v>62</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>171</v>
@@ -3617,13 +3623,13 @@
         <v>68</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>184</v>
@@ -3643,13 +3649,13 @@
         <v>74</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>188</v>
@@ -3669,13 +3675,13 @@
         <v>86</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>177</v>
@@ -3695,13 +3701,13 @@
         <v>100</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>153</v>
@@ -3721,13 +3727,13 @@
         <v>109</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>136</v>
@@ -3747,13 +3753,13 @@
         <v>112</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>130</v>
@@ -3773,13 +3779,13 @@
         <v>106</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>124</v>
@@ -3799,13 +3805,13 @@
         <v>97</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>115</v>
@@ -3825,13 +3831,13 @@
         <v>74</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>106</v>
@@ -3851,13 +3857,13 @@
         <v>60</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>103</v>
@@ -3877,13 +3883,13 @@
         <v>60</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>106</v>
@@ -3903,13 +3909,13 @@
         <v>60</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>115</v>
@@ -3929,13 +3935,13 @@
         <v>60</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>115</v>
@@ -3955,13 +3961,13 @@
         <v>77</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>109</v>
@@ -3981,13 +3987,13 @@
         <v>106</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>97</v>
@@ -4007,13 +4013,13 @@
         <v>106</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>74</v>
@@ -4033,13 +4039,13 @@
         <v>74</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>62</v>
@@ -4059,13 +4065,13 @@
         <v>143</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>65</v>
@@ -4085,13 +4091,13 @@
         <v>74</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>62</v>
@@ -4111,13 +4117,13 @@
         <v>65</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>57</v>
@@ -4137,13 +4143,13 @@
         <v>396</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>51</v>
@@ -4163,13 +4169,13 @@
         <v>127</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>32</v>
@@ -4189,13 +4195,13 @@
         <v>46</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>32</v>
@@ -4215,13 +4221,13 @@
         <v>46</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>35</v>
@@ -4241,13 +4247,13 @@
         <v>46</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>35</v>
@@ -4267,13 +4273,13 @@
         <v>60</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>35</v>
@@ -4293,13 +4299,13 @@
         <v>74</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>37</v>
@@ -4319,13 +4325,13 @@
         <v>51</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>40</v>
@@ -4345,13 +4351,13 @@
         <v>40</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>43</v>
@@ -4371,13 +4377,13 @@
         <v>37</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>46</v>
@@ -4397,13 +4403,13 @@
         <v>32</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="H85" s="1" t="s">
         <v>48</v>
@@ -4423,13 +4429,13 @@
         <v>29</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>48</v>
@@ -4449,13 +4455,13 @@
         <v>26</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>57</v>
@@ -4475,13 +4481,13 @@
         <v>29</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>62</v>
@@ -4501,13 +4507,13 @@
         <v>35</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>65</v>
@@ -4527,13 +4533,13 @@
         <v>37</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>74</v>
@@ -4553,13 +4559,13 @@
         <v>37</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>83</v>
@@ -4579,13 +4585,13 @@
         <v>146</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>93</v>
@@ -4605,13 +4611,13 @@
         <v>143</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>62</v>
@@ -4631,13 +4637,13 @@
         <v>122</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>40</v>
@@ -4657,13 +4663,13 @@
         <v>143</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>40</v>
@@ -4683,13 +4689,13 @@
         <v>83</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>40</v>
@@ -4709,13 +4715,13 @@
         <v>62</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>48</v>
@@ -4735,13 +4741,13 @@
         <v>29</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>57</v>
@@ -4761,13 +4767,13 @@
         <v>29</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>57</v>
@@ -4787,13 +4793,13 @@
         <v>166</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>89</v>
@@ -4813,13 +4819,13 @@
         <v>143</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>103</v>
@@ -4839,13 +4845,13 @@
         <v>91</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>106</v>
@@ -4865,13 +4871,13 @@
         <v>62</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="H103" s="1" t="s">
         <v>124</v>
@@ -4891,13 +4897,13 @@
         <v>93</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="H104" s="1" t="s">
         <v>127</v>
@@ -4917,13 +4923,13 @@
         <v>97</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="H105" s="1" t="s">
         <v>122</v>
@@ -4943,13 +4949,13 @@
         <v>103</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="H106" s="1" t="s">
         <v>109</v>
@@ -4969,13 +4975,13 @@
         <v>103</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="H107" s="1" t="s">
         <v>103</v>
@@ -4995,13 +5001,13 @@
         <v>93</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="H108" s="1" t="s">
         <v>103</v>
@@ -5021,13 +5027,13 @@
         <v>89</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="H109" s="1" t="s">
         <v>86</v>
@@ -5047,13 +5053,13 @@
         <v>62</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H110" s="1" t="s">
         <v>65</v>
@@ -5073,13 +5079,13 @@
         <v>40</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="H111" s="1" t="s">
         <v>62</v>
@@ -5099,13 +5105,13 @@
         <v>29</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H112" s="1" t="s">
         <v>60</v>
@@ -5125,13 +5131,13 @@
         <v>26</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="H113" s="1" t="s">
         <v>57</v>
@@ -5151,13 +5157,13 @@
         <v>26</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="H114" s="1" t="s">
         <v>57</v>
@@ -5177,13 +5183,13 @@
         <v>32</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H115" s="1" t="s">
         <v>57</v>
@@ -5203,13 +5209,13 @@
         <v>40</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="H116" s="1" t="s">
         <v>60</v>
@@ -5229,13 +5235,13 @@
         <v>54</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="H117" s="1" t="s">
         <v>74</v>
@@ -5255,13 +5261,13 @@
         <v>86</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="H118" s="1" t="s">
         <v>51</v>
@@ -5281,13 +5287,13 @@
         <v>68</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="H119" s="1" t="s">
         <v>43</v>
@@ -5307,13 +5313,13 @@
         <v>166</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="H120" s="1" t="s">
         <v>43</v>
@@ -5333,13 +5339,13 @@
         <v>122</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="H121" s="1" t="s">
         <v>51</v>
@@ -5359,13 +5365,13 @@
         <v>153</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="H122" s="1" t="s">
         <v>57</v>
@@ -5385,13 +5391,13 @@
         <v>51</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="H123" s="1" t="s">
         <v>65</v>
@@ -5411,13 +5417,13 @@
         <v>136</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>51</v>
@@ -5437,13 +5443,13 @@
         <v>103</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="H125" s="1" t="s">
         <v>65</v>
@@ -5463,13 +5469,13 @@
         <v>169</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H126" s="1" t="s">
         <v>71</v>
@@ -5489,13 +5495,13 @@
         <v>166</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="H127" s="1" t="s">
         <v>91</v>
@@ -5515,13 +5521,13 @@
         <v>159</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="H128" s="1" t="s">
         <v>97</v>
@@ -5541,13 +5547,13 @@
         <v>143</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="H129" s="1" t="s">
         <v>100</v>
@@ -5567,13 +5573,13 @@
         <v>133</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="H130" s="1" t="s">
         <v>89</v>
@@ -5593,13 +5599,13 @@
         <v>124</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="H131" s="1" t="s">
         <v>71</v>
@@ -5619,13 +5625,13 @@
         <v>117</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="H132" s="1" t="s">
         <v>68</v>
@@ -5645,13 +5651,13 @@
         <v>162</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="H133" s="1" t="s">
         <v>65</v>
@@ -5671,13 +5677,13 @@
         <v>103</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="H134" s="1" t="s">
         <v>65</v>
@@ -5697,13 +5703,13 @@
         <v>57</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="H135" s="1" t="s">
         <v>71</v>
@@ -5723,13 +5729,13 @@
         <v>48</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H136" s="1" t="s">
         <v>80</v>
@@ -5749,13 +5755,13 @@
         <v>48</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="H137" s="1" t="s">
         <v>86</v>
@@ -5775,7 +5781,7 @@
         <v>62</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>139</v>
@@ -5801,13 +5807,13 @@
         <v>68</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="H139" s="1" t="s">
         <v>77</v>
@@ -5827,13 +5833,13 @@
         <v>89</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="H140" s="1" t="s">
         <v>100</v>
@@ -5853,13 +5859,13 @@
         <v>97</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="H141" s="1" t="s">
         <v>93</v>
@@ -5879,13 +5885,13 @@
         <v>106</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="H142" s="1" t="s">
         <v>62</v>
@@ -5905,13 +5911,13 @@
         <v>109</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H143" s="1" t="s">
         <v>54</v>
@@ -5931,13 +5937,13 @@
         <v>255</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H144" s="1" t="s">
         <v>54</v>
@@ -5957,13 +5963,13 @@
         <v>148</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="H145" s="1" t="s">
         <v>51</v>
@@ -5983,13 +5989,13 @@
         <v>173</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H146" s="1" t="s">
         <v>68</v>
@@ -6009,13 +6015,13 @@
         <v>159</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="H147" s="1" t="s">
         <v>74</v>
@@ -6035,13 +6041,13 @@
         <v>143</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="H148" s="1" t="s">
         <v>74</v>
@@ -6061,13 +6067,13 @@
         <v>143</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="H149" s="1" t="s">
         <v>68</v>
@@ -6087,13 +6093,13 @@
         <v>143</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="H150" s="1" t="s">
         <v>74</v>
@@ -6113,13 +6119,13 @@
         <v>146</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="H151" s="1" t="s">
         <v>133</v>
@@ -6139,13 +6145,13 @@
         <v>156</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="H152" s="1" t="s">
         <v>146</v>
@@ -6162,16 +6168,16 @@
         <v>392</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="H153" s="1" t="s">
         <v>148</v>
@@ -6191,13 +6197,13 @@
         <v>194</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="H154" s="1" t="s">
         <v>148</v>
@@ -6217,13 +6223,13 @@
         <v>197</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H155" s="1" t="s">
         <v>151</v>
@@ -6243,13 +6249,13 @@
         <v>197</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="H156" s="1" t="s">
         <v>156</v>
@@ -6269,13 +6275,13 @@
         <v>188</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="H157" s="1" t="s">
         <v>130</v>
@@ -6295,13 +6301,13 @@
         <v>188</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="H158" s="1" t="s">
         <v>112</v>
@@ -6321,13 +6327,13 @@
         <v>186</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H159" s="1" t="s">
         <v>106</v>
@@ -6347,13 +6353,13 @@
         <v>162</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="H160" s="1" t="s">
         <v>109</v>
@@ -6373,13 +6379,13 @@
         <v>162</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="H161" s="1" t="s">
         <v>112</v>
@@ -6399,13 +6405,13 @@
         <v>162</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="H162" s="1" t="s">
         <v>106</v>
@@ -6425,13 +6431,13 @@
         <v>164</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="H163" s="1" t="s">
         <v>106</v>
@@ -6451,13 +6457,13 @@
         <v>164</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H164" s="1" t="s">
         <v>97</v>
@@ -6477,13 +6483,13 @@
         <v>166</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="H165" s="1" t="s">
         <v>86</v>
@@ -6503,13 +6509,13 @@
         <v>166</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="H166" s="1" t="s">
         <v>71</v>
@@ -6529,13 +6535,13 @@
         <v>166</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="H167" s="1" t="s">
         <v>74</v>
@@ -6555,13 +6561,13 @@
         <v>197</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H168" s="1" t="s">
         <v>100</v>
@@ -6581,16 +6587,42 @@
         <v>212</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>139</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="H169" s="1" t="s">
         <v>103</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A170" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="H170" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
